--- a/code/extracted_data_final_v9.xlsx
+++ b/code/extracted_data_final_v9.xlsx
@@ -464,20 +464,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026_07_14_18_26_49_11_case01_T0_P0.png</t>
+          <t>2026_07_10_14_16_08_11_case01_T0_P0.png</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>62.049</v>
+        <v>58.631</v>
       </c>
       <c r="D2" t="n">
-        <v>14.64</v>
+        <v>15.22</v>
       </c>
       <c r="E2" t="n">
-        <v>1.204</v>
+        <v>1.137</v>
       </c>
       <c r="F2" t="n">
-        <v>1.367</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="3">
@@ -486,20 +486,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026_07_14_18_41_12_11_case01_T0_P0.png</t>
+          <t>2026_07_10_14_31_52_11_case01_T0_P0.png</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>62.299</v>
+        <v>58.162</v>
       </c>
       <c r="D3" t="n">
-        <v>14.38</v>
+        <v>13.45</v>
       </c>
       <c r="E3" t="n">
-        <v>1.145</v>
+        <v>1.132</v>
       </c>
       <c r="F3" t="n">
-        <v>1.315</v>
+        <v>1.269</v>
       </c>
     </row>
     <row r="4">
@@ -508,20 +508,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026_07_14_19_43_51_11_case01_T0_P0.png</t>
+          <t>2026_07_10_14_45_47_11_case01_T0_P0.png</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>62.152</v>
+        <v>58.44</v>
       </c>
       <c r="D4" t="n">
-        <v>13.7</v>
+        <v>15.31</v>
       </c>
       <c r="E4" t="n">
-        <v>1.14</v>
+        <v>1.082</v>
       </c>
       <c r="F4" t="n">
-        <v>1.304</v>
+        <v>1.213</v>
       </c>
     </row>
     <row r="5">
@@ -530,20 +530,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026_07_15_07_39_59_11_case01_T0_P0.png</t>
+          <t>2026_07_10_14_59_46_11_case01_T0_P0.png</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>61.635</v>
+        <v>58.836</v>
       </c>
       <c r="D5" t="n">
-        <v>15.71</v>
+        <v>15.88</v>
       </c>
       <c r="E5" t="n">
-        <v>1.112</v>
+        <v>1.081</v>
       </c>
       <c r="F5" t="n">
-        <v>1.282</v>
+        <v>1.209</v>
       </c>
     </row>
     <row r="6">
@@ -552,20 +552,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026_07_15_07_57_03_11_case01_T0_P0.png</t>
+          <t>2026_07_10_15_17_18_11_case01_T0_P0.png</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>61.744</v>
+        <v>58.15</v>
       </c>
       <c r="D6" t="n">
-        <v>14.32</v>
+        <v>15.16</v>
       </c>
       <c r="E6" t="n">
-        <v>1.134</v>
+        <v>1.107</v>
       </c>
       <c r="F6" t="n">
-        <v>1.306</v>
+        <v>1.239</v>
       </c>
     </row>
   </sheetData>
@@ -620,21 +620,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026_07_14_18_38_00_11_case12_T32_P0.png</t>
+          <t>2026_07_10_14_26_54_11_case12_T32_P0.png</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.838</v>
+        <v>17.494</v>
       </c>
       <c r="D2" t="n">
-        <v>14.65</v>
+        <v>15.3</v>
       </c>
       <c r="E2" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2.689</v>
-      </c>
+        <v>2.113</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -642,21 +640,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026_07_14_18_52_24_11_case12_T32_P0.png</t>
+          <t>2026_07_10_14_42_38_11_case12_T32_P0.png</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.924</v>
+        <v>17.349</v>
       </c>
       <c r="D3" t="n">
-        <v>14.36</v>
+        <v>13.42</v>
       </c>
       <c r="E3" t="n">
-        <v>2.074</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2.63</v>
-      </c>
+        <v>2.122</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -664,21 +660,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026_07_14_19_55_03_11_case12_T32_P0.png</t>
+          <t>2026_07_10_14_56_34_11_case12_T32_P0.png</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.869</v>
+        <v>17.422</v>
       </c>
       <c r="D4" t="n">
-        <v>13.74</v>
+        <v>15.32</v>
       </c>
       <c r="E4" t="n">
-        <v>2.043</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2.576</v>
-      </c>
+        <v>2.083</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -686,21 +680,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026_07_15_07_51_09_11_case12_T32_P0.png</t>
+          <t>2026_07_10_15_10_32_11_case12_T32_P0.png</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.729</v>
+        <v>17.547</v>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>15.97</v>
       </c>
       <c r="E5" t="n">
-        <v>2.201</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2.695</v>
-      </c>
+        <v>2.053</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -708,21 +700,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026_07_15_08_08_14_11_case12_T32_P0.png</t>
+          <t>2026_07_10_15_28_03_11_case12_T32_P0.png</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.762</v>
+        <v>17.341</v>
       </c>
       <c r="D6" t="n">
-        <v>14.38</v>
+        <v>15.18</v>
       </c>
       <c r="E6" t="n">
-        <v>2.093</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2.637</v>
-      </c>
+        <v>2.102</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -776,21 +766,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026_07_14_18_38_45_11_case13_T40_P0.png</t>
+          <t>2026_07_10_14_27_38_11_case13_T40_P0.png</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.675</v>
+        <v>17.49</v>
       </c>
       <c r="D2" t="n">
-        <v>14.69</v>
+        <v>15.35</v>
       </c>
       <c r="E2" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="F2" t="n">
-        <v>3.084</v>
-      </c>
+        <v>2.095</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -798,21 +786,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026_07_14_18_53_08_11_case13_T40_P0.png</t>
+          <t>2026_07_10_14_43_23_11_case13_T40_P0.png</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.75</v>
+        <v>17.351</v>
       </c>
       <c r="D3" t="n">
-        <v>14.3</v>
+        <v>13.47</v>
       </c>
       <c r="E3" t="n">
-        <v>2.437</v>
-      </c>
-      <c r="F3" t="n">
-        <v>3.026</v>
-      </c>
+        <v>2.102</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -820,21 +806,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026_07_14_19_55_48_11_case13_T40_P0.png</t>
+          <t>2026_07_10_14_57_18_11_case13_T40_P0.png</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.703</v>
+        <v>17.429</v>
       </c>
       <c r="D4" t="n">
-        <v>13.75</v>
+        <v>15.35</v>
       </c>
       <c r="E4" t="n">
-        <v>2.376</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2.949</v>
-      </c>
+        <v>2.048</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -842,21 +826,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026_07_15_07_51_53_11_case13_T40_P0.png</t>
+          <t>2026_07_10_15_11_17_11_case13_T40_P0.png</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.565</v>
+        <v>17.549</v>
       </c>
       <c r="D5" t="n">
-        <v>15.01</v>
+        <v>15.95</v>
       </c>
       <c r="E5" t="n">
-        <v>2.531</v>
-      </c>
-      <c r="F5" t="n">
-        <v>3.067</v>
-      </c>
+        <v>2.04</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -864,21 +846,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026_07_15_08_08_58_11_case13_T40_P0.png</t>
+          <t>2026_07_10_15_28_48_11_case13_T40_P0.png</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.597</v>
+        <v>17.342</v>
       </c>
       <c r="D6" t="n">
-        <v>14.39</v>
+        <v>15.17</v>
       </c>
       <c r="E6" t="n">
-        <v>2.476</v>
-      </c>
-      <c r="F6" t="n">
-        <v>3.053</v>
-      </c>
+        <v>2.081</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -932,20 +912,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026_07_14_18_28_35_11_case02_T2_P0.png</t>
+          <t>2026_07_10_14_17_47_11_case02_T2_P0.png</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>62.036</v>
+        <v>58.62</v>
       </c>
       <c r="D2" t="n">
-        <v>14.6</v>
+        <v>15.27</v>
       </c>
       <c r="E2" t="n">
-        <v>1.203</v>
+        <v>1.14</v>
       </c>
       <c r="F2" t="n">
-        <v>1.364</v>
+        <v>1.261</v>
       </c>
     </row>
     <row r="3">
@@ -954,20 +934,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026_07_14_18_42_59_11_case02_T2_P0.png</t>
+          <t>2026_07_10_14_33_31_11_case02_T2_P0.png</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>62.319</v>
+        <v>58.157</v>
       </c>
       <c r="D3" t="n">
-        <v>14.43</v>
+        <v>13.43</v>
       </c>
       <c r="E3" t="n">
-        <v>1.16</v>
+        <v>1.135</v>
       </c>
       <c r="F3" t="n">
-        <v>1.328</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="4">
@@ -976,20 +956,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026_07_14_19_45_38_11_case02_T2_P0.png</t>
+          <t>2026_07_10_14_47_27_11_case02_T2_P0.png</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>62.157</v>
+        <v>58.417</v>
       </c>
       <c r="D4" t="n">
-        <v>13.78</v>
+        <v>15.35</v>
       </c>
       <c r="E4" t="n">
-        <v>1.137</v>
+        <v>1.085</v>
       </c>
       <c r="F4" t="n">
-        <v>1.302</v>
+        <v>1.214</v>
       </c>
     </row>
     <row r="5">
@@ -998,20 +978,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026_07_15_07_41_45_11_case02_T2_P0.png</t>
+          <t>2026_07_10_15_01_25_11_case02_T2_P0.png</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>61.648</v>
+        <v>58.833</v>
       </c>
       <c r="D5" t="n">
-        <v>14.82</v>
+        <v>15.87</v>
       </c>
       <c r="E5" t="n">
-        <v>1.018</v>
+        <v>1.088</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2</v>
+        <v>1.214</v>
       </c>
     </row>
     <row r="6">
@@ -1020,20 +1000,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026_07_15_07_58_49_11_case02_T2_P0.png</t>
+          <t>2026_07_10_15_18_57_11_case02_T2_P0.png</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>61.755</v>
+        <v>58.146</v>
       </c>
       <c r="D6" t="n">
-        <v>14.37</v>
+        <v>15.1</v>
       </c>
       <c r="E6" t="n">
-        <v>1.141</v>
+        <v>1.118</v>
       </c>
       <c r="F6" t="n">
-        <v>1.311</v>
+        <v>1.249</v>
       </c>
     </row>
   </sheetData>
@@ -1088,20 +1068,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026_07_14_18_30_15_11_case03_T4_P1.png</t>
+          <t>2026_07_10_14_19_26_11_case03_T4_P1.png</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>57.354</v>
+        <v>58.855</v>
       </c>
       <c r="D2" t="n">
-        <v>14.62</v>
+        <v>15.2</v>
       </c>
       <c r="E2" t="n">
-        <v>1.258</v>
+        <v>1.134</v>
       </c>
       <c r="F2" t="n">
-        <v>1.45</v>
+        <v>1.254</v>
       </c>
     </row>
     <row r="3">
@@ -1110,20 +1090,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026_07_14_18_44_38_11_case03_T4_P1.png</t>
+          <t>2026_07_10_14_35_10_11_case03_T4_P1.png</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>57.617</v>
+        <v>58.366</v>
       </c>
       <c r="D3" t="n">
-        <v>14.38</v>
+        <v>13.39</v>
       </c>
       <c r="E3" t="n">
-        <v>1.217</v>
+        <v>1.145</v>
       </c>
       <c r="F3" t="n">
-        <v>1.418</v>
+        <v>1.279</v>
       </c>
     </row>
     <row r="4">
@@ -1132,20 +1112,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026_07_14_19_47_17_11_case03_T4_P1.png</t>
+          <t>2026_07_10_14_49_06_11_case03_T4_P1.png</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>57.45</v>
+        <v>58.626</v>
       </c>
       <c r="D4" t="n">
-        <v>13.8</v>
+        <v>15.35</v>
       </c>
       <c r="E4" t="n">
-        <v>1.189</v>
+        <v>1.098</v>
       </c>
       <c r="F4" t="n">
-        <v>1.382</v>
+        <v>1.227</v>
       </c>
     </row>
     <row r="5">
@@ -1154,20 +1134,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026_07_15_07_43_25_11_case03_T4_P1.png</t>
+          <t>2026_07_10_15_03_05_11_case03_T4_P1.png</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>56.976</v>
+        <v>59.042</v>
       </c>
       <c r="D5" t="n">
-        <v>14.9</v>
+        <v>15.93</v>
       </c>
       <c r="E5" t="n">
-        <v>1.258</v>
+        <v>1.079</v>
       </c>
       <c r="F5" t="n">
-        <v>1.442</v>
+        <v>1.208</v>
       </c>
     </row>
     <row r="6">
@@ -1176,20 +1156,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026_07_15_08_00_29_11_case03_T4_P1.png</t>
+          <t>2026_07_10_15_20_36_11_case03_T4_P1.png</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>57.092</v>
+        <v>58.366</v>
       </c>
       <c r="D6" t="n">
-        <v>14.33</v>
+        <v>15.14</v>
       </c>
       <c r="E6" t="n">
-        <v>1.194</v>
+        <v>1.113</v>
       </c>
       <c r="F6" t="n">
-        <v>1.397</v>
+        <v>1.246</v>
       </c>
     </row>
   </sheetData>
@@ -1244,21 +1224,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026_07_14_18_31_54_11_case04_T6_P0.png</t>
+          <t>2026_07_10_14_20_57_11_case04_T6_P0.png</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40.674</v>
+        <v>50.164</v>
       </c>
       <c r="D2" t="n">
-        <v>14.59</v>
+        <v>15.27</v>
       </c>
       <c r="E2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1.347</v>
-      </c>
+        <v>1.13</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1266,21 +1244,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026_07_14_18_46_18_11_case04_T6_P0.png</t>
+          <t>2026_07_10_14_36_41_11_case04_T6_P0.png</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>40.856</v>
+        <v>49.744</v>
       </c>
       <c r="D3" t="n">
-        <v>14.39</v>
+        <v>13.42</v>
       </c>
       <c r="E3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1.285</v>
-      </c>
+        <v>1.112</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1288,21 +1264,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026_07_14_19_48_57_11_case04_T6_P0.png</t>
+          <t>2026_07_10_14_50_37_11_case04_T6_P0.png</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>40.743</v>
+        <v>49.961</v>
       </c>
       <c r="D4" t="n">
-        <v>13.74</v>
+        <v>15.41</v>
       </c>
       <c r="E4" t="n">
-        <v>1.101</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1.272</v>
-      </c>
+        <v>1.068</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1310,21 +1284,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026_07_15_07_45_03_11_case04_T6_P0.png</t>
+          <t>2026_07_10_15_04_35_11_case04_T6_P0.png</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>40.397</v>
+        <v>50.316</v>
       </c>
       <c r="D5" t="n">
-        <v>14.94</v>
+        <v>15.95</v>
       </c>
       <c r="E5" t="n">
-        <v>1.179</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1.341</v>
-      </c>
+        <v>1.064</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1332,21 +1304,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026_07_15_08_02_08_11_case04_T6_P0.png</t>
+          <t>2026_07_10_15_22_07_11_case04_T6_P0.png</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>40.467</v>
+        <v>49.737</v>
       </c>
       <c r="D6" t="n">
-        <v>14.35</v>
+        <v>15.19</v>
       </c>
       <c r="E6" t="n">
-        <v>1.092</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1.27</v>
-      </c>
+        <v>1.09</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1400,20 +1370,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026_07_14_18_33_21_11_case05_T8_P0.png</t>
+          <t>2026_07_10_14_22_23_11_case05_T8_P0.png</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40.631</v>
+        <v>50.136</v>
       </c>
       <c r="D2" t="n">
-        <v>14.62</v>
+        <v>15.25</v>
       </c>
       <c r="E2" t="n">
-        <v>1.188</v>
+        <v>1.107</v>
       </c>
       <c r="F2" t="n">
-        <v>1.35</v>
+        <v>1.231</v>
       </c>
     </row>
     <row r="3">
@@ -1422,20 +1392,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026_07_14_18_47_44_11_case05_T8_P0.png</t>
+          <t>2026_07_10_14_38_07_11_case05_T8_P0.png</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>40.808</v>
+        <v>49.725</v>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>13.46</v>
       </c>
       <c r="E3" t="n">
-        <v>1.118</v>
+        <v>1.127</v>
       </c>
       <c r="F3" t="n">
-        <v>1.294</v>
+        <v>1.261</v>
       </c>
     </row>
     <row r="4">
@@ -1444,20 +1414,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026_07_14_19_50_23_11_case05_T8_P0.png</t>
+          <t>2026_07_10_14_52_03_11_case05_T8_P0.png</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>40.695</v>
+        <v>49.965</v>
       </c>
       <c r="D4" t="n">
-        <v>13.73</v>
+        <v>15.35</v>
       </c>
       <c r="E4" t="n">
-        <v>1.067</v>
+        <v>1.071</v>
       </c>
       <c r="F4" t="n">
-        <v>1.242</v>
+        <v>1.204</v>
       </c>
     </row>
     <row r="5">
@@ -1466,20 +1436,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026_07_15_07_46_29_11_case05_T8_P0.png</t>
+          <t>2026_07_10_15_06_01_11_case05_T8_P0.png</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>40.371</v>
+        <v>50.299</v>
       </c>
       <c r="D5" t="n">
-        <v>15.01</v>
+        <v>15.97</v>
       </c>
       <c r="E5" t="n">
-        <v>1.17</v>
+        <v>1.055</v>
       </c>
       <c r="F5" t="n">
-        <v>1.331</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="6">
@@ -1488,20 +1458,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026_07_15_08_03_34_11_case05_T8_P0.png</t>
+          <t>2026_07_10_15_23_33_11_case05_T8_P0.png</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>40.424</v>
+        <v>49.723</v>
       </c>
       <c r="D6" t="n">
-        <v>14.32</v>
+        <v>15.2</v>
       </c>
       <c r="E6" t="n">
-        <v>1.12</v>
+        <v>1.094</v>
       </c>
       <c r="F6" t="n">
-        <v>1.292</v>
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>
@@ -1556,20 +1526,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026_07_14_18_34_40_11_case06_T10_P0.png</t>
+          <t>2026_07_10_14_23_34_11_case06_T10_P0.png</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40.654</v>
+        <v>40.841</v>
       </c>
       <c r="D2" t="n">
-        <v>14.66</v>
+        <v>15.28</v>
       </c>
       <c r="E2" t="n">
-        <v>1.233</v>
+        <v>1.262</v>
       </c>
       <c r="F2" t="n">
-        <v>1.402</v>
+        <v>1.439</v>
       </c>
     </row>
     <row r="3">
@@ -1578,20 +1548,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026_07_14_18_49_03_11_case06_T10_P0.png</t>
+          <t>2026_07_10_14_39_18_11_case06_T10_P0.png</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>40.842</v>
+        <v>40.496</v>
       </c>
       <c r="D3" t="n">
-        <v>14.37</v>
+        <v>13.47</v>
       </c>
       <c r="E3" t="n">
-        <v>1.151</v>
+        <v>1.265</v>
       </c>
       <c r="F3" t="n">
-        <v>1.333</v>
+        <v>1.461</v>
       </c>
     </row>
     <row r="4">
@@ -1600,20 +1570,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026_07_14_19_51_42_11_case06_T10_P0.png</t>
+          <t>2026_07_10_14_53_14_11_case06_T10_P0.png</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>40.742</v>
+        <v>40.681</v>
       </c>
       <c r="D4" t="n">
-        <v>13.78</v>
+        <v>15.32</v>
       </c>
       <c r="E4" t="n">
-        <v>1.098</v>
+        <v>1.224</v>
       </c>
       <c r="F4" t="n">
-        <v>1.281</v>
+        <v>1.413</v>
       </c>
     </row>
     <row r="5">
@@ -1622,20 +1592,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026_07_15_07_47_48_11_case06_T10_P0.png</t>
+          <t>2026_07_10_15_07_12_11_case06_T10_P0.png</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>40.398</v>
+        <v>40.951</v>
       </c>
       <c r="D5" t="n">
-        <v>14.93</v>
+        <v>15.89</v>
       </c>
       <c r="E5" t="n">
-        <v>1.212</v>
+        <v>1.204</v>
       </c>
       <c r="F5" t="n">
-        <v>1.377</v>
+        <v>1.394</v>
       </c>
     </row>
     <row r="6">
@@ -1644,20 +1614,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026_07_15_08_04_53_11_case06_T10_P0.png</t>
+          <t>2026_07_10_15_24_43_11_case06_T10_P0.png</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>40.463</v>
+        <v>40.495</v>
       </c>
       <c r="D6" t="n">
-        <v>14.35</v>
+        <v>15.16</v>
       </c>
       <c r="E6" t="n">
-        <v>1.139</v>
+        <v>1.23</v>
       </c>
       <c r="F6" t="n">
-        <v>1.322</v>
+        <v>1.428</v>
       </c>
     </row>
   </sheetData>
@@ -1712,17 +1682,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026_07_14_18_35_38_11_case08_T18_P0.png</t>
+          <t>2026_07_10_14_24_32_11_case08_T18_P0.png</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>32.201</v>
+        <v>32.32</v>
       </c>
       <c r="D2" t="n">
-        <v>34.54</v>
+        <v>34.29</v>
       </c>
       <c r="E2" t="n">
-        <v>1.253</v>
+        <v>1.418</v>
       </c>
       <c r="F2" t="inlineStr"/>
     </row>
@@ -1732,17 +1702,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026_07_14_18_50_02_11_case08_T18_P0.png</t>
+          <t>2026_07_10_14_40_16_11_case08_T18_P0.png</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>32.345</v>
+        <v>32.049</v>
       </c>
       <c r="D3" t="n">
-        <v>33.18</v>
+        <v>35.71</v>
       </c>
       <c r="E3" t="n">
-        <v>1.186</v>
+        <v>1.419</v>
       </c>
       <c r="F3" t="inlineStr"/>
     </row>
@@ -1752,17 +1722,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026_07_14_19_52_41_11_case08_T18_P0.png</t>
+          <t>2026_07_10_14_54_12_11_case08_T18_P0.png</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>32.261</v>
+        <v>32.196</v>
       </c>
       <c r="D4" t="n">
-        <v>33</v>
+        <v>34.05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.134</v>
+        <v>1.364</v>
       </c>
       <c r="F4" t="inlineStr"/>
     </row>
@@ -1772,17 +1742,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026_07_15_07_48_47_11_case08_T18_P0.png</t>
+          <t>2026_07_10_15_08_11_11_case08_T18_P0.png</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>31.986</v>
+        <v>32.418</v>
       </c>
       <c r="D5" t="n">
-        <v>35.78</v>
+        <v>36.12</v>
       </c>
       <c r="E5" t="n">
-        <v>1.295</v>
+        <v>1.38</v>
       </c>
       <c r="F5" t="inlineStr"/>
     </row>
@@ -1792,17 +1762,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026_07_15_08_05_52_11_case08_T18_P0.png</t>
+          <t>2026_07_10_15_25_42_11_case08_T18_P0.png</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>32.047</v>
+        <v>32.041</v>
       </c>
       <c r="D6" t="n">
-        <v>35.55</v>
+        <v>35.72</v>
       </c>
       <c r="E6" t="n">
-        <v>1.187</v>
+        <v>1.406</v>
       </c>
       <c r="F6" t="inlineStr"/>
     </row>
@@ -1858,19 +1828,21 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026_07_14_18_36_27_11_case09_T22_P1.png</t>
+          <t>2026_07_10_14_25_21_11_case09_T22_P1.png</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>23.151</v>
+        <v>23.179</v>
       </c>
       <c r="D2" t="n">
-        <v>34.3</v>
+        <v>35.37</v>
       </c>
       <c r="E2" t="n">
-        <v>1.615</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>1.605</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.92</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1878,19 +1850,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026_07_14_18_50_50_11_case09_T22_P1.png</t>
+          <t>2026_07_10_14_41_05_11_case09_T22_P1.png</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23.251</v>
+        <v>22.985</v>
       </c>
       <c r="D3" t="n">
-        <v>34.87</v>
+        <v>33.11</v>
       </c>
       <c r="E3" t="n">
-        <v>1.533</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>1.628</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.965</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1898,19 +1872,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026_07_14_19_53_29_11_case09_T22_P1.png</t>
+          <t>2026_07_10_14_55_01_11_case09_T22_P1.png</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23.195</v>
+        <v>23.096</v>
       </c>
       <c r="D4" t="n">
-        <v>33.46</v>
+        <v>37.11</v>
       </c>
       <c r="E4" t="n">
-        <v>1.498</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>1.585</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.916</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1918,19 +1894,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026_07_15_07_49_36_11_case09_T22_P1.png</t>
+          <t>2026_07_10_15_08_59_11_case09_T22_P1.png</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>23</v>
+        <v>23.24</v>
       </c>
       <c r="D5" t="n">
-        <v>35.12</v>
+        <v>37.11</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>1.596</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.918</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1938,19 +1916,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026_07_15_08_06_41_11_case09_T22_P1.png</t>
+          <t>2026_07_10_15_26_30_11_case09_T22_P1.png</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23.037</v>
+        <v>22.977</v>
       </c>
       <c r="D6" t="n">
-        <v>35.6</v>
+        <v>35.9</v>
       </c>
       <c r="E6" t="n">
-        <v>1.553</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
+        <v>1.586</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.924</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2004,19 +1984,21 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026_07_14_18_37_15_11_case11_T28_P0.png</t>
+          <t>2026_07_10_14_26_09_11_case11_T28_P0.png</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>23.025</v>
+        <v>23.207</v>
       </c>
       <c r="D2" t="n">
-        <v>33.88</v>
+        <v>36</v>
       </c>
       <c r="E2" t="n">
-        <v>1.634</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>1.56</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.857</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2024,19 +2006,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026_07_14_18_51_39_11_case11_T28_P0.png</t>
+          <t>2026_07_10_14_41_53_11_case11_T28_P0.png</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23.134</v>
+        <v>23.018</v>
       </c>
       <c r="D3" t="n">
-        <v>32.37</v>
+        <v>34.13</v>
       </c>
       <c r="E3" t="n">
-        <v>1.539</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>1.535</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.856</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2044,19 +2028,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026_07_14_19_54_18_11_case11_T28_P0.png</t>
+          <t>2026_07_10_14_55_49_11_case11_T28_P0.png</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23.064</v>
+        <v>23.113</v>
       </c>
       <c r="D4" t="n">
-        <v>32.35</v>
+        <v>38.14</v>
       </c>
       <c r="E4" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>1.536</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.845</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -2064,19 +2050,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026_07_15_07_50_24_11_case11_T28_P0.png</t>
+          <t>2026_07_10_15_09_48_11_case11_T28_P0.png</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.879</v>
+        <v>23.276</v>
       </c>
       <c r="D5" t="n">
-        <v>34.2</v>
+        <v>38.62</v>
       </c>
       <c r="E5" t="n">
-        <v>1.656</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>1.503</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.817</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -2084,19 +2072,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026_07_15_08_07_29_11_case11_T28_P0.png</t>
+          <t>2026_07_10_15_27_19_11_case11_T28_P0.png</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.922</v>
+        <v>23.009</v>
       </c>
       <c r="D6" t="n">
-        <v>35.6</v>
+        <v>35.97</v>
       </c>
       <c r="E6" t="n">
-        <v>1.569</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
+        <v>1.532</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.849</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
